--- a/artfynd/A 40939-2021 artfynd.xlsx
+++ b/artfynd/A 40939-2021 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 40939-2021 artfynd.xlsx
+++ b/artfynd/A 40939-2021 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,37 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>102899841</v>
+        <v>102899849</v>
       </c>
       <c r="B2" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80433</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>220787</v>
+        <v>2081</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Skrovellav</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria scrobiculata</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Scop.) DC.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -715,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>624329.5378051496</v>
+        <v>624335</v>
       </c>
       <c r="R2" t="n">
-        <v>7210192.858265447</v>
+        <v>7210040</v>
       </c>
       <c r="S2" t="n">
         <v>10</v>
@@ -748,21 +743,11 @@
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA2" t="inlineStr">
         <is>
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD2" t="b">
         <v>0</v>
       </c>
@@ -771,6 +756,21 @@
       </c>
       <c r="AG2" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ2" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO2" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
@@ -791,37 +791,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>102899844</v>
+        <v>102899845</v>
       </c>
       <c r="B3" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>97231</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -831,10 +826,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>624348.9114585029</v>
+        <v>624387</v>
       </c>
       <c r="R3" t="n">
-        <v>7210145.367336446</v>
+        <v>7210088</v>
       </c>
       <c r="S3" t="n">
         <v>10</v>
@@ -864,21 +859,11 @@
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD3" t="b">
         <v>0</v>
       </c>
@@ -887,21 +872,6 @@
       </c>
       <c r="AG3" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ3" t="inlineStr">
-        <is>
-          <t>sälg</t>
-        </is>
-      </c>
-      <c r="AK3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
-      </c>
-      <c r="AO3" t="inlineStr">
-        <is>
-          <t>Salix caprea</t>
-        </is>
       </c>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
@@ -922,37 +892,32 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>102899842</v>
+        <v>102899843</v>
       </c>
       <c r="B4" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -962,10 +927,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>624342.0124588225</v>
+        <v>624342</v>
       </c>
       <c r="R4" t="n">
-        <v>7210158.213549233</v>
+        <v>7210154</v>
       </c>
       <c r="S4" t="n">
         <v>10</v>
@@ -995,21 +960,11 @@
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA4" t="inlineStr">
         <is>
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD4" t="b">
         <v>0</v>
       </c>
@@ -1018,6 +973,21 @@
       </c>
       <c r="AG4" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ4" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO4" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
@@ -1038,37 +1008,32 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>102899840</v>
+        <v>102899844</v>
       </c>
       <c r="B5" t="n">
-        <v>96334</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>220787</v>
+        <v>6458</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1078,10 +1043,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>624284.1053791055</v>
+        <v>624349</v>
       </c>
       <c r="R5" t="n">
-        <v>7210224.432930402</v>
+        <v>7210145</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1111,21 +1076,11 @@
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AD5" t="b">
         <v>0</v>
       </c>
@@ -1134,6 +1089,21 @@
       </c>
       <c r="AG5" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ5" t="inlineStr">
+        <is>
+          <t>sälg</t>
+        </is>
+      </c>
+      <c r="AK5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
+      </c>
+      <c r="AO5" t="inlineStr">
+        <is>
+          <t>Salix caprea</t>
+        </is>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
@@ -1154,15 +1124,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>102899843</v>
+        <v>102899848</v>
       </c>
       <c r="B6" t="n">
-        <v>78569</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>80432</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1194,10 +1159,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>624342.1889645453</v>
+        <v>624336</v>
       </c>
       <c r="R6" t="n">
-        <v>7210153.984104624</v>
+        <v>7210041</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1227,19 +1192,9 @@
           <t>2022-08-12</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2022-08-12</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1278,6 +1233,511 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>102899840</v>
+      </c>
+      <c r="B7" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Lill-Granliden/Björnberget, Grundfors, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>624284</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7210225</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>102899841</v>
+      </c>
+      <c r="B8" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Lill-Granliden/Björnberget, Grundfors, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>624329</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7210193</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>102899842</v>
+      </c>
+      <c r="B9" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Lill-Granliden/Björnberget, Grundfors, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>624342</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7210158</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>102899846</v>
+      </c>
+      <c r="B10" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Lill-Granliden/Björnberget, Grundfors, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>624342</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7210055</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr">
+        <is>
+          <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>102899847</v>
+      </c>
+      <c r="B11" t="n">
+        <v>99118</v>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Lill-Granliden/Björnberget, Grundfors, Storuman, Ly lm</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>624335</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7210044</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västerbotten</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Storuman</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Lycksele lappmark</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Stensele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2022-08-12</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Carl Jansson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr">
         <is>
           <t>Länsstyrelsens naturvärdesinventeringar i Västerbottens län</t>
         </is>
